--- a/BorosilicateGlass/ScratchWork.xlsx
+++ b/BorosilicateGlass/ScratchWork.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\PAH_Absorption_Energy\SimulationsSoftwareProgramsCode\VOCC_Simulation\BorosilicateGlass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933A113E-6632-4828-8BEF-700A257B2F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FB78C7A-DD7F-4327-88BD-373E453CC3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-12910" yWindow="-21710" windowWidth="38620" windowHeight="21100" xr2:uid="{3F4C9C1C-6576-4DC5-97F5-48720945B5F4}"/>
+    <workbookView xWindow="44520" yWindow="-13305" windowWidth="28800" windowHeight="15375" xr2:uid="{3F4C9C1C-6576-4DC5-97F5-48720945B5F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -726,8 +726,40 @@
       <c r="D16">
         <v>2.12561</v>
       </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="G16">
+        <v>23</v>
+      </c>
+      <c r="H16">
+        <v>11</v>
+      </c>
+      <c r="I16">
+        <v>217</v>
+      </c>
+      <c r="J16">
+        <v>87</v>
+      </c>
+      <c r="K16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="G17">
+        <v>3</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>-2</v>
+      </c>
+      <c r="J17">
+        <v>4</v>
+      </c>
+      <c r="K17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B18">
         <v>0.49209999999999998</v>
       </c>
@@ -737,8 +769,32 @@
       <c r="D18">
         <v>3.8976600000000001</v>
       </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="G18">
+        <f>G17*G16</f>
+        <v>69</v>
+      </c>
+      <c r="H18">
+        <f t="shared" ref="H18:K18" si="1">H17*H16</f>
+        <v>11</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="1"/>
+        <v>-434</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="1"/>
+        <v>348</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L18">
+        <f>SUM(G18:K18)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B20">
         <v>0.26150000000000001</v>
       </c>
